--- a/rendu/annexes/157443_Voeffray_Lucielle_Journal.xlsx
+++ b/rendu/annexes/157443_Voeffray_Lucielle_Journal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\rendu\annexes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D582E5-20C3-467A-B494-C2BCEB30428F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52532B75-2FC9-42C9-A4FF-48CEF414DE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$89</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -201,34 +201,6 @@
     <t>Créer Template</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Playbook qui reçoit un 403: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF92D050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Problème et solution au point 6.2.4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Playbook ne trouve pas le template: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF92D050"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Problème et solution au point 6.2.3</t>
-    </r>
-  </si>
-  <si>
     <t>J'ai passé 2h sur une erreur d'orthographe T-T Vraiment je me fatigue</t>
   </si>
   <si>
@@ -313,6 +285,52 @@
   <si>
     <t>Qu'est-ce que je déteste passer une journée entière sur de la documentation !! C'est vraiment difficile de rester concentrée… Je sais, d'expérience amère, que c'est le plus important. Mais quel ennui !</t>
   </si>
+  <si>
+    <t>Contrôle des critères d'évaluation</t>
+  </si>
+  <si>
+    <t>Approfondisssement du guide utilisateur</t>
+  </si>
+  <si>
+    <t>Même commentaire que le 2 juin, ça avance mais c'est d'un ennui.</t>
+  </si>
+  <si>
+    <t>Rendu de la documentation</t>
+  </si>
+  <si>
+    <t>Création des PDFs et finitions du dossier de rendu</t>
+  </si>
+  <si>
+    <t>Et voilà, fini. Ce projet aura été une formalité plutôt qu'un défis, et ça me rassure grandement</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Playbook ne trouve pas le template: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Problème et solution au point 6.2.3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Playbook qui reçoit un 403: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Problème et solution au point 6.2.4</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -322,7 +340,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -390,12 +408,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FF92D050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -694,6 +706,50 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -706,16 +762,68 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -726,137 +834,19 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1372,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1383,117 +1373,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="46"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="42"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
+      <c r="A6" s="35">
         <v>46153</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="23"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="22" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="22" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="23"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1506,57 +1496,57 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="16"/>
+      <c r="B14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
     </row>
     <row r="15" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <v>46154</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="23"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="23"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="23"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1569,117 +1559,117 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="26" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
+      <c r="A21" s="15">
         <v>46157</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="23"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="23"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="22" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="22" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="23"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
-      <c r="B25" s="22" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="23"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="22" t="s">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="23"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="23"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="22" t="s">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="23"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="8">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="39"/>
-      <c r="B29" s="29" t="s">
+      <c r="A29" s="36"/>
+      <c r="B29" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="30"/>
+      <c r="C29" s="47"/>
       <c r="D29" s="13">
         <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="36" t="s">
+      <c r="A30" s="16"/>
+      <c r="B30" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="37"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="2" t="s">
         <v>6</v>
       </c>
@@ -1692,77 +1682,77 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="21"/>
     </row>
     <row r="33" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="17">
+      <c r="A33" s="15">
         <v>46160</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="37"/>
+      <c r="C33" s="24"/>
       <c r="D33" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="18"/>
-      <c r="B34" s="22" t="s">
+      <c r="A34" s="16"/>
+      <c r="B34" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="23"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="22" t="s">
+      <c r="A35" s="16"/>
+      <c r="B35" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="23"/>
+      <c r="C35" s="18"/>
       <c r="D35" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="22" t="s">
+      <c r="A36" s="16"/>
+      <c r="B36" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="23"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="18"/>
-      <c r="B37" s="22" t="s">
+      <c r="A37" s="16"/>
+      <c r="B37" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="23"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="18"/>
-      <c r="B38" s="22" t="s">
+      <c r="A38" s="16"/>
+      <c r="B38" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="23"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1775,47 +1765,47 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
     </row>
     <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="17">
+      <c r="A41" s="15">
         <v>46161</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="23"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="18"/>
-      <c r="B42" s="22" t="s">
+      <c r="A42" s="16"/>
+      <c r="B42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="23"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="23"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="18"/>
       <c r="D43" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
@@ -1828,47 +1818,47 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="27"/>
     </row>
     <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="17">
+      <c r="A46" s="15">
         <v>46163</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="21"/>
+      <c r="B46" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="45"/>
       <c r="D46" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="21"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="45"/>
       <c r="D47" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="23"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="18"/>
       <c r="D48" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="18"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="2" t="s">
         <v>6</v>
       </c>
@@ -1881,59 +1871,59 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="16"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="17">
+      <c r="A51" s="15">
         <v>46164</v>
       </c>
-      <c r="B51" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" s="32"/>
+      <c r="B51" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="40"/>
       <c r="D51" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="18"/>
-      <c r="B52" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="23"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="18"/>
       <c r="D52" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="18"/>
-      <c r="B53" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="37"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="24"/>
       <c r="D53" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="18"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="25"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="38"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="18"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="2" t="s">
         <v>6</v>
       </c>
@@ -1946,59 +1936,59 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="16"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="17">
+      <c r="A58" s="15">
         <v>46171</v>
       </c>
-      <c r="B58" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58" s="21"/>
+      <c r="B58" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="45"/>
       <c r="D58" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="18"/>
-      <c r="B59" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="23"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="18"/>
       <c r="D59" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="18"/>
-      <c r="B60" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" s="23"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="18"/>
       <c r="D60" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="18"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="23"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
       <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="18"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="25"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="38"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="18"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="2" t="s">
         <v>6</v>
       </c>
@@ -2011,85 +2001,85 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="19"/>
-      <c r="B64" s="14" t="s">
+      <c r="A64" s="22"/>
+      <c r="B64" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27"/>
+    </row>
+    <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B65" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="15"/>
-      <c r="D64" s="16"/>
-    </row>
-    <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="17">
-        <v>46174</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C65" s="32"/>
+      <c r="C65" s="40"/>
       <c r="D65" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="18"/>
-      <c r="B66" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" s="23"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" s="18"/>
       <c r="D66" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="18"/>
-      <c r="B67" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C67" s="23"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="18"/>
       <c r="D67" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="18"/>
-      <c r="B68" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C68" s="23"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" s="18"/>
       <c r="D68" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C69" s="23"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="18"/>
       <c r="D69" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="18"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="23"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="18"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="18"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="23"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="18"/>
       <c r="D71" s="8"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="18"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="23"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
       <c r="D72" s="8"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="18"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="2" t="s">
         <v>6</v>
       </c>
@@ -2102,63 +2092,63 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="18"/>
-      <c r="B74" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C74" s="34"/>
-      <c r="D74" s="35"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="42"/>
+      <c r="D74" s="43"/>
     </row>
     <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="17">
+      <c r="A75" s="15">
         <v>46175</v>
       </c>
-      <c r="B75" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C75" s="32"/>
+      <c r="B75" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="40"/>
       <c r="D75" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="18"/>
-      <c r="B76" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C76" s="23"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="18"/>
       <c r="D76" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="18"/>
-      <c r="B77" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C77" s="23"/>
+      <c r="A77" s="16"/>
+      <c r="B77" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="18"/>
       <c r="D77" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="18"/>
-      <c r="B78" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C78" s="23"/>
+      <c r="A78" s="16"/>
+      <c r="B78" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" s="18"/>
       <c r="D78" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="18"/>
-      <c r="B79" s="22"/>
-      <c r="C79" s="23"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="38"/>
       <c r="D79" s="8"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="18"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="2" t="s">
         <v>6</v>
       </c>
@@ -2171,86 +2161,205 @@
       </c>
     </row>
     <row r="81" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="19"/>
-      <c r="B81" s="14" t="s">
+      <c r="A81" s="22"/>
+      <c r="B81" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="26"/>
+      <c r="D81" s="27"/>
+    </row>
+    <row r="82" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="15">
+        <v>46178</v>
+      </c>
+      <c r="B82" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82" s="40"/>
+      <c r="D82" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="16"/>
+      <c r="B83" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C83" s="18"/>
+      <c r="D83" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="16"/>
+      <c r="B84" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="15"/>
-      <c r="D81" s="16"/>
-    </row>
-    <row r="82" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="17">
-        <v>46178</v>
-      </c>
-      <c r="B82" s="31"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="7"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="18"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="8"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="18"/>
-      <c r="B84" s="22"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="8"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="18"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="8"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="18"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="8"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="18"/>
-      <c r="B87" s="2" t="s">
+      <c r="A85" s="16"/>
+      <c r="B85" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D87" s="9">
-        <f>SUM(D82:D86)</f>
+      <c r="D85" s="9">
+        <f>SUM(D82:D84)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="22"/>
+      <c r="B86" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C86" s="26"/>
+      <c r="D86" s="27"/>
+    </row>
+    <row r="87" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="15">
+        <v>46181</v>
+      </c>
+      <c r="B87" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" s="40"/>
+      <c r="D87" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="16"/>
+      <c r="B88" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88" s="18"/>
+      <c r="D88" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="16"/>
+      <c r="B89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="9">
+        <f>SUM(D87:D88)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="22"/>
+      <c r="B90" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C90" s="26"/>
+      <c r="D90" s="27"/>
+    </row>
+    <row r="91" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="11"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="12">
+        <f>D13+D19+D31+D39+D44+D49+D56+D63+D73+D80+D85+D89</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="14" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="19"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="16"/>
-    </row>
-    <row r="89" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="11"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="12">
-        <f>D13+D19+D31+D39+D44+D49+D56+D63+D73+D80+D87</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B90" s="47"/>
-      <c r="C90" s="47"/>
-      <c r="D90" s="47"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="A90:D90"/>
+  <mergeCells count="90">
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A75:A81"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A15:A20"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
@@ -2266,143 +2375,63 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A21:A32"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="A65:A74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="A46:A50"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="A51:A57"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A75:A81"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="A82:A88"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="A58:A64"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B64:D64"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D13 D15:D19 D21">
-    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="13" priority="26" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21 D6:D13 D15:D19">
-    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21:D31 D33:D39 D41:D44 D46:D49">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Terminé">
+  <conditionalFormatting sqref="D21:D31 D33:D39 D41:D44 D46:D49 D87:D89 D82:D85">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:D56">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D63">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D58)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D65:D73">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D65)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:D80">
-    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="3" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D75)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D75)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D82:D87">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D82)))</formula>
+  <conditionalFormatting sqref="D91">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D82)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D89">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D89)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D89)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D91)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2415,7 +2444,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="50" max="16383" man="1"/>
-    <brk id="89" max="3" man="1"/>
+    <brk id="91" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
